--- a/data/trans_orig/P70B_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P70B_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según como se adapta su horario laboral a sus compromisos sociales y familiares fuera del trabajo en 2023</t>
+          <t>Población según como se adapta su horario laboral a sus compromisos sociales y familiares fuera del trabajo en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23119</t>
+          <t>23132</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>740</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26201</t>
+          <t>29171</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>23175</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11712</t>
+          <t>12145</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>28462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71280</t>
+          <t>70508</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95309</t>
+          <t>95277</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36623</t>
+          <t>36124</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55985</t>
+          <t>55688</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114255</t>
+          <t>113918</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>144944</t>
+          <t>144970</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,15%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25675</t>
+          <t>25705</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46871</t>
+          <t>47928</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13678</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28694</t>
+          <t>29732</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44756</t>
+          <t>44077</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71799</t>
+          <t>71038</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>18147</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47573</t>
+          <t>49448</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12377</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27075</t>
+          <t>28240</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>34958</t>
+          <t>35545</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>68393</t>
+          <t>71799</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88296</t>
+          <t>102566</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>230058</t>
+          <t>225724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93287</t>
+          <t>87453</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143226</t>
+          <t>139916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>211733</t>
+          <t>204659</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>353182</t>
+          <t>352215</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>816200</t>
+          <t>817298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1128365</t>
+          <t>1118266</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>419411</t>
+          <t>419774</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>599080</t>
+          <t>597570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1332789</t>
+          <t>1325943</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1702182</t>
+          <t>1717573</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>127778</t>
+          <t>133079</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>301959</t>
+          <t>304704</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>199389</t>
+          <t>199445</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>412602</t>
+          <t>420875</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>365874</t>
+          <t>352373</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>655049</t>
+          <t>661059</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20925</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17752</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14799</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34215</t>
+          <t>34134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15397</t>
+          <t>15370</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37506</t>
+          <t>40086</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31606</t>
+          <t>32313</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54022</t>
+          <t>55828</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>52662</t>
+          <t>51716</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>82380</t>
+          <t>81920</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>230792</t>
+          <t>229786</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>277039</t>
+          <t>278713</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>231368</t>
+          <t>229722</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>268426</t>
+          <t>267822</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>472912</t>
+          <t>473549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>529939</t>
+          <t>532788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>60,06%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137946</t>
+          <t>137475</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>182953</t>
+          <t>181559</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119067</t>
+          <t>120056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153462</t>
+          <t>155475</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>268757</t>
+          <t>270038</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>325152</t>
+          <t>323983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27214</t>
+          <t>28041</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61117</t>
+          <t>62838</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24852</t>
+          <t>26412</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57245</t>
+          <t>57913</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59308</t>
+          <t>61151</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104914</t>
+          <t>108390</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138462</t>
+          <t>132048</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>255773</t>
+          <t>256874</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>138627</t>
+          <t>138916</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>194794</t>
+          <t>193902</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>295563</t>
+          <t>299526</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>435144</t>
+          <t>437252</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1152759</t>
+          <t>1144837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1481423</t>
+          <t>1541638</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>704536</t>
+          <t>707995</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>894721</t>
+          <t>899207</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1952145</t>
+          <t>1950785</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2348206</t>
+          <t>2375479</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>69,43%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>296865</t>
+          <t>266267</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>513993</t>
+          <t>518218</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>355689</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>590245</t>
+          <t>584535</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>694288</t>
+          <t>687095</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1010923</t>
+          <t>995065</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70B_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P70B_2023-Estudios-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>741</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23132</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29171</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>15779</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23175</t>
+          <t>26285</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12145</t>
+          <t>16072</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>18772</t>
+          <t>24982</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11912</t>
+          <t>15914</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28462</t>
+          <t>37512</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>83460</t>
+          <t>100066</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70508</t>
+          <t>84199</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95277</t>
+          <t>113336</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>54603</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36124</t>
+          <t>45476</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55688</t>
+          <t>62327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>130642</t>
+          <t>154669</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>113918</t>
+          <t>137915</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>144970</t>
+          <t>171141</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,77%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35782</t>
+          <t>47349</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25705</t>
+          <t>36025</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47928</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20519</t>
+          <t>23342</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>16844</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29732</t>
+          <t>32139</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>56302</t>
+          <t>70691</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44077</t>
+          <t>55860</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71038</t>
+          <t>86990</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>212712</t>
+          <t>252535</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212712</t>
+          <t>252535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212712</t>
+          <t>252535</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32863</t>
+          <t>37957</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18147</t>
+          <t>26245</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49448</t>
+          <t>53775</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19106</t>
+          <t>20259</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12473</t>
+          <t>13084</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28240</t>
+          <t>28621</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>51969</t>
+          <t>58216</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35545</t>
+          <t>43398</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71799</t>
+          <t>75655</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>176910</t>
+          <t>186094</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102566</t>
+          <t>157347</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>225724</t>
+          <t>216866</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>118857</t>
+          <t>129096</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87453</t>
+          <t>109869</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139916</t>
+          <t>147158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>295767</t>
+          <t>315190</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>204659</t>
+          <t>281330</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>352215</t>
+          <t>349618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>928521</t>
+          <t>766971</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>817298</t>
+          <t>725141</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1118266</t>
+          <t>805474</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>542355</t>
+          <t>574629</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>419774</t>
+          <t>548364</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>597570</t>
+          <t>601377</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1470876</t>
+          <t>1341600</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1325943</t>
+          <t>1293846</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1717573</t>
+          <t>1392153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>63,01%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>240658</t>
+          <t>276092</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133079</t>
+          <t>244412</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>304704</t>
+          <t>309488</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>262147</t>
+          <t>218418</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>199445</t>
+          <t>196693</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>420875</t>
+          <t>243317</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>502806</t>
+          <t>494510</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>352373</t>
+          <t>454519</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>661059</t>
+          <t>538822</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1378952</t>
+          <t>1267114</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1378952</t>
+          <t>1267114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1378952</t>
+          <t>1267114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>942465</t>
+          <t>942403</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>942465</t>
+          <t>942403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>942465</t>
+          <t>942403</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2321417</t>
+          <t>2209516</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2321417</t>
+          <t>2209516</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2321417</t>
+          <t>2209516</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>6896</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21163</t>
+          <t>25865</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>13397</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18266</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>22618</t>
+          <t>26871</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>17956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34134</t>
+          <t>40899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23859</t>
+          <t>24873</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15370</t>
+          <t>16238</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>43244</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42093</t>
+          <t>44184</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32313</t>
+          <t>33885</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55828</t>
+          <t>57120</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>65952</t>
+          <t>69057</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>51716</t>
+          <t>54744</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>81920</t>
+          <t>87970</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>252850</t>
+          <t>272104</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>229786</t>
+          <t>247870</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>278713</t>
+          <t>295825</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>249184</t>
+          <t>276425</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>229722</t>
+          <t>257808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>267822</t>
+          <t>296101</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>502034</t>
+          <t>548530</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>473549</t>
+          <t>515432</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>532788</t>
+          <t>578597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -2202,67 +2202,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>160277</t>
+          <t>178916</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137475</t>
+          <t>154273</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>181559</t>
+          <t>201792</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>31,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>147719</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>130022</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>165212</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>30,66%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,49%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>136281</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>120056</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>155475</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>31,06%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>296559</t>
+          <t>326635</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270038</t>
+          <t>297882</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>323983</t>
+          <t>356890</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,75%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>448441</t>
+          <t>489366</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>448441</t>
+          <t>489366</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>448441</t>
+          <t>489366</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>438721</t>
+          <t>481725</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>438721</t>
+          <t>481725</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>438721</t>
+          <t>481725</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>887162</t>
+          <t>971092</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>887162</t>
+          <t>971092</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>887162</t>
+          <t>971092</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>45073</t>
+          <t>52171</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28041</t>
+          <t>36355</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62838</t>
+          <t>71757</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>36509</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26412</t>
+          <t>25703</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57913</t>
+          <t>46065</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>81582</t>
+          <t>87279</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>70406</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108390</t>
+          <t>110008</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>212874</t>
+          <t>226746</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132048</t>
+          <t>195113</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256874</t>
+          <t>264514</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>167616</t>
+          <t>182483</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>138916</t>
+          <t>161528</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>193902</t>
+          <t>207199</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>380491</t>
+          <t>409229</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>299526</t>
+          <t>368824</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>437252</t>
+          <t>454525</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1264830</t>
+          <t>1139141</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1144837</t>
+          <t>1093901</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1541638</t>
+          <t>1187997</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>838722</t>
+          <t>905658</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>707995</t>
+          <t>872428</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>899207</t>
+          <t>941828</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2103552</t>
+          <t>2044799</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1950785</t>
+          <t>1981225</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2375479</t>
+          <t>2104371</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>61,3%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>436718</t>
+          <t>502357</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>266267</t>
+          <t>460549</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>518218</t>
+          <t>548408</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>418948</t>
+          <t>389479</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>355453</t>
+          <t>357099</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>584535</t>
+          <t>420031</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>855666</t>
+          <t>891836</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>687095</t>
+          <t>836763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>995065</t>
+          <t>945870</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1959496</t>
+          <t>1920415</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1959496</t>
+          <t>1920415</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1959496</t>
+          <t>1920415</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1461795</t>
+          <t>1512728</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1461795</t>
+          <t>1512728</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1461795</t>
+          <t>1512728</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3421291</t>
+          <t>3433143</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3421291</t>
+          <t>3433143</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3421291</t>
+          <t>3433143</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
